--- a/Sensitivity_SSIM_Pirate.xlsx
+++ b/Sensitivity_SSIM_Pirate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4AE664B-90DE-4FA3-93F2-D6F4413279EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3275C4F-468A-4C84-B503-87F207723C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86223BD2-13D8-48B6-B0FE-EC980E27CC11}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8ECDFE1F-9D70-488D-9C23-951EF702657F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C790F94A-1058-4A7B-9A47-58DF2F3EFC49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5AC3F06-CD32-4F9E-B90A-6D6331C69B3B}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2507857A-EF7F-4C52-B709-9C39FD8F1E17}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F3FDE8F-D1BB-483D-A632-0D879B226977}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5D2F7B8-1919-40C3-BEEF-BF5245347857}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82189474-3D2E-4508-92D3-4C4D631B348A}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
